--- a/TestData/LV_T2009_GiftLogRecipientsExceedsYearlyGiftAllowanceGreaterThan100ForCurrencyTypeAustralianDollar.xlsx
+++ b/TestData/LV_T2009_GiftLogRecipientsExceedsYearlyGiftAllowanceGreaterThan100ForCurrencyTypeAustralianDollar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305B1762-BF8E-4EA7-BE3B-CD69E329E6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558546E8-5FAE-4025-AA0A-92E0A848A092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t>ConvertedGiftValue</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Melissa Zatta</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>NEW GIFT AMT YTD</t>
+  </si>
+  <si>
+    <t>100</t>
   </si>
 </sst>
 </file>
@@ -473,7 +473,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -489,12 +489,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -512,12 +512,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -596,10 +596,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -617,7 +617,7 @@
         <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
         <v>20</v>

--- a/TestData/LV_T2009_GiftLogRecipientsExceedsYearlyGiftAllowanceGreaterThan100ForCurrencyTypeAustralianDollar.xlsx
+++ b/TestData/LV_T2009_GiftLogRecipientsExceedsYearlyGiftAllowanceGreaterThan100ForCurrencyTypeAustralianDollar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558546E8-5FAE-4025-AA0A-92E0A848A092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6642805B-39B7-430A-92DF-75BCB14F3D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t>ConvertedGiftValue</t>
   </si>
   <si>
-    <t>Melissa Zatta</t>
-  </si>
-  <si>
     <t>Giftlog Contact</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
   </si>
   <si>
     <t>100</t>
+  </si>
+  <si>
+    <t>Julie Carthane</t>
   </si>
 </sst>
 </file>
@@ -473,7 +473,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -489,12 +489,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -512,12 +512,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -596,10 +596,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -617,7 +617,7 @@
         <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M2" t="s">
         <v>20</v>

--- a/TestData/LV_T2009_GiftLogRecipientsExceedsYearlyGiftAllowanceGreaterThan100ForCurrencyTypeAustralianDollar.xlsx
+++ b/TestData/LV_T2009_GiftLogRecipientsExceedsYearlyGiftAllowanceGreaterThan100ForCurrencyTypeAustralianDollar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6642805B-39B7-430A-92DF-75BCB14F3D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08510F9-9031-4957-98BC-65ABA7065587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -126,10 +126,10 @@
     <t>NEW GIFT AMT YTD</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>Julie Carthane</t>
+  </si>
+  <si>
+    <t>180</t>
   </si>
 </sst>
 </file>
@@ -473,7 +473,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -596,10 +596,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
